--- a/docs/tables.xlsx
+++ b/docs/tables.xlsx
@@ -8,14 +8,17 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\boram1288\orange\arch\test-p\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9CBD5B0-BA8E-4D9F-A1EC-A0DAA340E458}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{772F6CAA-2AE0-450C-8723-41706E27D937}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{566D5FF2-664D-49E6-8694-5714426ADE65}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="5" xr2:uid="{566D5FF2-664D-49E6-8694-5714426ADE65}"/>
   </bookViews>
   <sheets>
     <sheet name="StakeHolder" sheetId="3" r:id="rId1"/>
     <sheet name="VOS" sheetId="1" r:id="rId2"/>
     <sheet name="UC (정제)" sheetId="2" r:id="rId3"/>
+    <sheet name="FR" sheetId="4" r:id="rId4"/>
+    <sheet name="CONST" sheetId="5" r:id="rId5"/>
+    <sheet name="QA" sheetId="6" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,17 +39,80 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="143">
+  <si>
+    <t>품질 속성</t>
+  </si>
+  <si>
+    <t>성능 (실시간 처리)</t>
+  </si>
+  <si>
+    <t>성능 (통신 오버헤드)</t>
+  </si>
+  <si>
+    <t>자원 효율</t>
+  </si>
+  <si>
+    <t>시험 용이성</t>
+  </si>
+  <si>
+    <t>성능 (HW IP 공유 오버헤드)</t>
+  </si>
+  <si>
+    <t>QA-01</t>
+  </si>
+  <si>
+    <t>QA-02</t>
+  </si>
+  <si>
+    <t>QA-03</t>
+  </si>
+  <si>
+    <t>QA-04</t>
+  </si>
+  <si>
+    <t>QA-05</t>
+  </si>
+  <si>
+    <t>QA-06</t>
+  </si>
+  <si>
+    <t>QA-07</t>
+  </si>
+  <si>
+    <t>QA-08</t>
+  </si>
+  <si>
+    <t>QA-09</t>
+  </si>
   <si>
     <t>ID</t>
   </si>
   <si>
+    <t>요구사항</t>
+  </si>
+  <si>
     <t>설명</t>
   </si>
   <si>
+    <t>출처 VOS</t>
+  </si>
+  <si>
+    <t>관련 UC</t>
+  </si>
+  <si>
+    <t>FR-01</t>
+  </si>
+  <si>
+    <t>VOS-01, VOS-07</t>
+  </si>
+  <si>
     <t>UC-01</t>
   </si>
   <si>
+    <t>FR-02</t>
+  </si>
+  <si>
     <t>다중 pVM 동시 운용</t>
   </si>
   <si>
@@ -56,24 +122,45 @@
     <t>UC-02</t>
   </si>
   <si>
+    <t>FR-03</t>
+  </si>
+  <si>
     <t>Camera/AI HW 공유 사용</t>
   </si>
   <si>
+    <t>VOS-02, VOS-08</t>
+  </si>
+  <si>
     <t>UC-03</t>
   </si>
   <si>
+    <t>FR-04</t>
+  </si>
+  <si>
+    <t>VOS-01, VOS-09</t>
+  </si>
+  <si>
     <t>UC-04</t>
   </si>
   <si>
+    <t>FR-05</t>
+  </si>
+  <si>
     <t>VOS-05</t>
   </si>
   <si>
     <t>UC-05</t>
   </si>
   <si>
+    <t>FR-06</t>
+  </si>
+  <si>
     <t>Secure OS ENC/DEC 명령 전송</t>
   </si>
   <si>
+    <t>VOS-11, VOS-12</t>
+  </si>
+  <si>
     <t>UC-06</t>
   </si>
   <si>
@@ -254,9 +341,6 @@
     <t>Secure Camera, Secure AI 등 복수 pVM을 독립적으로 동시에 운용한다</t>
   </si>
   <si>
-    <t>Camera/AI HW 하드웨어 가속을 Host와 pVM에서 동시에 사용한다</t>
-  </si>
-  <si>
     <t>도메인 간 보안 데이터 전송</t>
   </si>
   <si>
@@ -266,17 +350,472 @@
     <t>보안 Workload 동적 탑재</t>
   </si>
   <si>
-    <t>펌웨어 재배포 없이 신규 보안 Workload를 pVM에 동적으로 탑재한다</t>
-  </si>
-  <si>
-    <t>pVM 내 Secure OS에 암호화/복호화 명령을 전송한다</t>
+    <t>pVM의 생성/시작/정지/종료와 자원 할당/회수를 관리하는 기능을 제공한다.</t>
+  </si>
+  <si>
+    <t>Secure Camera, Secure AI 등 복수 pVM을 독립적으로 동시 운용하는 기능을 제공한다.</t>
+  </si>
+  <si>
+    <t>Camera/AI HW를 Host/pVM이 SW 중재로 공유하고, 사용 주체 전환 시 격리를 보장하는 기능을 제공한다.</t>
+  </si>
+  <si>
+    <t>pVM↔pVM, pVM↔Host 간 데이터를 비신뢰 주체에 노출 없이 전달하는 보안 채널 기능을 제공한다.</t>
+  </si>
+  <si>
+    <t>신규 보안 Workload를 재배포 없이 서명 검증 후 동적으로 pVM에 탑재하는 기능을 제공한다.</t>
+  </si>
+  <si>
+    <t>pVM내에서 ENC/DEC를 Secure OS에 전달하는 기능을 제공한다.</t>
+  </si>
+  <si>
+    <t>제약사항</t>
+  </si>
+  <si>
+    <t>Linux 네이티브</t>
+  </si>
+  <si>
+    <t>Android 스택에 의존하지 않고 Linux에서 네이티브로 동작한다.</t>
+  </si>
+  <si>
+    <t>CONST-02</t>
+  </si>
+  <si>
+    <t>pKVM 커널 전제</t>
+  </si>
+  <si>
+    <t>기 포팅된 pKVM(EL2)을 전제로, EL2 수정 없이 hypercall 범위 내에서 설계한다.</t>
+  </si>
+  <si>
+    <t>측정 방법</t>
+  </si>
+  <si>
+    <t>보안 (기밀성)</t>
+  </si>
+  <si>
+    <t>Host가 완전히 침해되어도 pVM 내 영상/모델/추론 데이터는 노출되지 않는다.</t>
+  </si>
+  <si>
+    <t>격리 메모리 노출 0건 (차단율 100%)</t>
+  </si>
+  <si>
+    <t>VOS-01, VOS-15</t>
+  </si>
+  <si>
+    <t>영상 입력이 유입될 때 Camera/AI HW 가속으로 격리 환경에서도 실시간 처리 속도를 만족한다.</t>
+  </si>
+  <si>
+    <t>30fps 유지, E2E 지연 100ms 이하, 비격리 대비 성능 저하 10% 이내 (가정치)</t>
+  </si>
+  <si>
+    <t>도메인 간 대용량 데이터 전달 시 통신 오버헤드가 실시간성을 해치지 않는다.</t>
+  </si>
+  <si>
+    <t>zero-copy 또는 프레임당 전달 지연 5ms 이하 (가정치)</t>
+  </si>
+  <si>
+    <t>보안 기능 활성화 시 메모리/전력 오버헤드가 탑재 가능 한도 이내로 유지된다.</t>
+  </si>
+  <si>
+    <t>추가 메모리 256MB 이하, 전력 증가 5% 이내 (가정치)</t>
+  </si>
+  <si>
+    <t>확장성</t>
+  </si>
+  <si>
+    <t>신규 Workload 추가 시 소스 수정 없이 패키징/탑재만으로 수용된다.</t>
+  </si>
+  <si>
+    <t>Framework 코어 수정 0 LoC, Workload 패키지 작성/탑재만으로 동작</t>
+  </si>
+  <si>
+    <t>변경 용이성 (Secure OS 이식)</t>
+  </si>
+  <si>
+    <t>Secure OS/Framework 버전이 변경될 때 정의된 인터페이스만으로 대응하고 재이식하지 않는다.</t>
+  </si>
+  <si>
+    <t>Secure OS 외 모듈의 수정 파일 0개</t>
+  </si>
+  <si>
+    <t>가용성</t>
+  </si>
+  <si>
+    <t>pVM이 비정상 종료/오동작해도 Host/다른 pVM/로봇 기본 동작은 유지된다.</t>
+  </si>
+  <si>
+    <t>Host/타 pVM 다운타임 0, 장애 pVM 재시작 3초 이내 (가정치)</t>
+  </si>
+  <si>
+    <t>격리 검증이 필요할 때 Host 침해를 모사한 시험으로 객관적으로 검증할 수 있다.</t>
+  </si>
+  <si>
+    <t>QA-01~03 자동화 시험 커버 100%, 회귀 시험 반복 실행 가능</t>
+  </si>
+  <si>
+    <t>Host/pVM이 HW IP를 동시 사용할 때 중재 오버헤드가 양쪽의 실시간 요구를 해치지 않는다.</t>
+  </si>
+  <si>
+    <t>목표 프레임율 유지(저하 10% 이내), 사용 주체 전환 오버헤드 1ms 이하 (가정치)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Camera/AI HW </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>하드웨어</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>가속을</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> Host</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>와</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> pVM</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>에서</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>사용한다</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>펌웨어</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>재배포</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>없이</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>신규</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> Workload</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>를</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> pVM</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>에</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>동적으로</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>탑재한다</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>pVM</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>에서</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> Secure OS</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>에</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>암호화</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>복호화</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>명령을</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>전송한다</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>CONST-01</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -304,6 +843,27 @@
       <family val="2"/>
       <charset val="129"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color rgb="FF000000"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color rgb="FF000000"/>
+      <name val="Segoe UI"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color rgb="FF000000"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <charset val="129"/>
     </font>
   </fonts>
   <fills count="2">
@@ -343,7 +903,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -353,10 +913,16 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -682,102 +1248,102 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A1" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="B1" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>39</v>
+      <c r="A1" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A2" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="B2" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="C2" s="4" t="s">
-        <v>41</v>
+      <c r="A2" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A3" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>42</v>
+      <c r="A3" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A4" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>43</v>
+      <c r="A4" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>71</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A5" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="C5" s="4" t="s">
+      <c r="A5" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A6" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A7" s="5" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A6" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A7" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="B7" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>47</v>
+      <c r="B7" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A8" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="B8" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="C8" s="4" t="s">
+      <c r="A8" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A9" s="5" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A9" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="B9" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="C9" s="4" t="s">
-        <v>49</v>
+      <c r="B9" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>77</v>
       </c>
     </row>
   </sheetData>
@@ -796,190 +1362,190 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A1" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="C1" s="3" t="s">
+      <c r="A1" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A2" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A3" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A4" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A5" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A6" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A7" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="B7" s="5" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A2" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="B2" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="C2" s="4" t="s">
+      <c r="C7" s="5" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A8" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="B8" s="5" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A3" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="C3" s="4" t="s">
+      <c r="C8" s="5" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A9" s="5" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A4" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="C4" s="4" t="s">
+      <c r="B9" s="5" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A5" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="C5" s="4" t="s">
+      <c r="C9" s="5" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A10" s="5" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A6" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="C6" s="4" t="s">
+      <c r="B10" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A11" s="5" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A7" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="B7" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="C7" s="4" t="s">
+      <c r="B11" s="5" t="s">
         <v>56</v>
       </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A8" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="B8" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="C8" s="4" t="s">
+      <c r="C11" s="5" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A12" s="5" t="s">
         <v>57</v>
       </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A9" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="B9" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="C9" s="4" t="s">
+      <c r="B12" s="5" t="s">
         <v>58</v>
       </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A10" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="B10" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="C10" s="4" t="s">
+      <c r="C12" s="5" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A13" s="5" t="s">
         <v>59</v>
       </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A11" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="B11" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="C11" s="4" t="s">
+      <c r="B13" s="5" t="s">
         <v>60</v>
       </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A12" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="B12" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="C12" s="4" t="s">
+      <c r="C13" s="5" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A14" s="5" t="s">
         <v>61</v>
       </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A13" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="B13" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="C13" s="4" t="s">
+      <c r="B14" s="5" t="s">
         <v>62</v>
       </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A14" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="B14" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="C14" s="4" t="s">
+      <c r="C14" s="5" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A15" s="5" t="s">
         <v>63</v>
       </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A15" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="B15" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="C15" s="4" t="s">
+      <c r="B15" s="5" t="s">
         <v>64</v>
       </c>
+      <c r="C15" s="5" t="s">
+        <v>92</v>
+      </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A16" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="B16" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="C16" s="4" t="s">
+      <c r="A16" s="5" t="s">
         <v>65</v>
       </c>
+      <c r="B16" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="C16" s="5" t="s">
+        <v>93</v>
+      </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A17" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="B17" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="C17" s="4" t="s">
-        <v>66</v>
+      <c r="A17" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="C17" s="5" t="s">
+        <v>94</v>
       </c>
     </row>
   </sheetData>
@@ -999,79 +1565,79 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
-        <v>67</v>
+        <v>95</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>68</v>
+        <v>96</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>1</v>
+        <v>17</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A2" s="2" t="s">
-        <v>2</v>
+        <v>22</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>69</v>
+        <v>97</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>70</v>
+        <v>98</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A3" s="2" t="s">
-        <v>5</v>
+        <v>26</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>71</v>
+        <v>99</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A4" s="2" t="s">
-        <v>7</v>
+        <v>30</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>6</v>
+        <v>28</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>72</v>
+        <v>139</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A5" s="2" t="s">
-        <v>8</v>
+        <v>33</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>73</v>
+        <v>100</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>74</v>
+        <v>101</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A6" s="2" t="s">
-        <v>10</v>
+        <v>36</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>76</v>
+        <v>102</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>140</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A7" s="2" t="s">
-        <v>12</v>
+        <v>40</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>11</v>
+        <v>38</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>77</v>
+        <v>141</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.4">
@@ -1118,6 +1684,386 @@
       <c r="A16" s="2"/>
       <c r="B16" s="2"/>
       <c r="C16" s="2"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A541DB4C-3518-4E9E-B674-29F56CE3873D}">
+  <dimension ref="A1:E7"/>
+  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="2" max="2" width="21" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="73.19921875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.796875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.296875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A2" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A3" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A4" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A5" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A6" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A7" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>40</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6B28AE17-5A65-4395-BC12-CB2558163A43}">
+  <dimension ref="A1:D3"/>
+  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="2" max="2" width="14.296875" customWidth="1"/>
+    <col min="3" max="3" width="54.5" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A2" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A3" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>55</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{291A8966-D248-40C5-810D-CDD92F7EB876}">
+  <dimension ref="A1:E10"/>
+  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="2" max="2" width="20.8984375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="67.19921875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="56.69921875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.796875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A2" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A3" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A4" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A5" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A6" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A7" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A8" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A9" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A10" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>45</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>

--- a/docs/tables.xlsx
+++ b/docs/tables.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\boram1288\orange\arch\test-p\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{772F6CAA-2AE0-450C-8723-41706E27D937}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E663518-DF6D-4800-92F7-3D3C4E45B3B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="5" xr2:uid="{566D5FF2-664D-49E6-8694-5714426ADE65}"/>
   </bookViews>
@@ -39,11 +39,26 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="143">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="215" uniqueCount="149">
   <si>
     <t>품질 속성</t>
   </si>
   <si>
+    <t>중요도</t>
+  </si>
+  <si>
+    <t>난이도</t>
+  </si>
+  <si>
+    <t>보안 (Host 침해 기밀성)</t>
+  </si>
+  <si>
+    <t>H</t>
+  </si>
+  <si>
+    <t>M</t>
+  </si>
+  <si>
     <t>성능 (실시간 처리)</t>
   </si>
   <si>
@@ -53,10 +68,7 @@
     <t>자원 효율</t>
   </si>
   <si>
-    <t>시험 용이성</t>
-  </si>
-  <si>
-    <t>성능 (HW IP 공유 오버헤드)</t>
+    <t>변경 용이성 (Secure OS 교체)</t>
   </si>
   <si>
     <t>QA-01</t>
@@ -386,76 +398,28 @@
     <t>기 포팅된 pKVM(EL2)을 전제로, EL2 수정 없이 hypercall 범위 내에서 설계한다.</t>
   </si>
   <si>
-    <t>측정 방법</t>
-  </si>
-  <si>
-    <t>보안 (기밀성)</t>
-  </si>
-  <si>
     <t>Host가 완전히 침해되어도 pVM 내 영상/모델/추론 데이터는 노출되지 않는다.</t>
   </si>
   <si>
-    <t>격리 메모리 노출 0건 (차단율 100%)</t>
-  </si>
-  <si>
-    <t>VOS-01, VOS-15</t>
-  </si>
-  <si>
     <t>영상 입력이 유입될 때 Camera/AI HW 가속으로 격리 환경에서도 실시간 처리 속도를 만족한다.</t>
   </si>
   <si>
-    <t>30fps 유지, E2E 지연 100ms 이하, 비격리 대비 성능 저하 10% 이내 (가정치)</t>
-  </si>
-  <si>
     <t>도메인 간 대용량 데이터 전달 시 통신 오버헤드가 실시간성을 해치지 않는다.</t>
   </si>
   <si>
-    <t>zero-copy 또는 프레임당 전달 지연 5ms 이하 (가정치)</t>
-  </si>
-  <si>
     <t>보안 기능 활성화 시 메모리/전력 오버헤드가 탑재 가능 한도 이내로 유지된다.</t>
   </si>
   <si>
-    <t>추가 메모리 256MB 이하, 전력 증가 5% 이내 (가정치)</t>
-  </si>
-  <si>
-    <t>확장성</t>
-  </si>
-  <si>
     <t>신규 Workload 추가 시 소스 수정 없이 패키징/탑재만으로 수용된다.</t>
   </si>
   <si>
-    <t>Framework 코어 수정 0 LoC, Workload 패키지 작성/탑재만으로 동작</t>
-  </si>
-  <si>
-    <t>변경 용이성 (Secure OS 이식)</t>
-  </si>
-  <si>
     <t>Secure OS/Framework 버전이 변경될 때 정의된 인터페이스만으로 대응하고 재이식하지 않는다.</t>
   </si>
   <si>
-    <t>Secure OS 외 모듈의 수정 파일 0개</t>
-  </si>
-  <si>
-    <t>가용성</t>
-  </si>
-  <si>
     <t>pVM이 비정상 종료/오동작해도 Host/다른 pVM/로봇 기본 동작은 유지된다.</t>
   </si>
   <si>
-    <t>Host/타 pVM 다운타임 0, 장애 pVM 재시작 3초 이내 (가정치)</t>
-  </si>
-  <si>
     <t>격리 검증이 필요할 때 Host 침해를 모사한 시험으로 객관적으로 검증할 수 있다.</t>
-  </si>
-  <si>
-    <t>QA-01~03 자동화 시험 커버 100%, 회귀 시험 반복 실행 가능</t>
-  </si>
-  <si>
-    <t>Host/pVM이 HW IP를 동시 사용할 때 중재 오버헤드가 양쪽의 실시간 요구를 해치지 않는다.</t>
-  </si>
-  <si>
-    <t>목표 프레임율 유지(저하 10% 이내), 사용 주체 전환 오버헤드 1ms 이하 (가정치)</t>
   </si>
   <si>
     <r>
@@ -809,13 +773,67 @@
   <si>
     <t>CONST-01</t>
     <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>우선순위</t>
+  </si>
+  <si>
+    <t>[침해 테스트 시험에서 pVM 소유 메모리로부터 읽힌 바이트 수 = 0건]</t>
+  </si>
+  <si>
+    <t>1순위</t>
+  </si>
+  <si>
+    <t>[전체 파이프라인에 대해서 (비격리 fps − 격리 fps) ÷ 비격리 fps ≤ 10%]</t>
+  </si>
+  <si>
+    <t>[도메인간 dma-buf버퍼 전달시 memcpy 호출 횟수 = 0회]</t>
+  </si>
+  <si>
+    <t>2순위</t>
+  </si>
+  <si>
+    <t>[(격리 메모리 − 비격리 메모리) ≤ 256MB, (격리 전력 − 비격리 전력) ÷ 비격리 전력 ≤ 5%]</t>
+  </si>
+  <si>
+    <t>3순위</t>
+  </si>
+  <si>
+    <t>확장성 (Workload 수용)</t>
+  </si>
+  <si>
+    <t>[Workload 추가 전후 git diff에서 Framework 코어 디렉터리 변경 라인 수 = 0 LoC]</t>
+  </si>
+  <si>
+    <t>[Secure OS 교체 전후 git diff에서 Secure OS 패키지 외부 변경 파일 수 = 0개]</t>
+  </si>
+  <si>
+    <t>가용성 (pVM 장애 격리)</t>
+  </si>
+  <si>
+    <t>[(Workload 서비스 재개 시각) − (장애 주입 시각) ≤ 3초]</t>
+  </si>
+  <si>
+    <t>시험 용이성 (격리 검증)</t>
+  </si>
+  <si>
+    <t>[(전체 공격 벡터 항목 − 미커버 항목) ÷ 전체 항목 = 100%]</t>
+  </si>
+  <si>
+    <t>보안 (HW 접근 격리)</t>
+  </si>
+  <si>
+    <t>Camera/AI HW 사용 주체 전환 시 배타적 접근이 항상 보장된다.</t>
+  </si>
+  <si>
+    <t>[S2MPU 권한 상태 로그에서 두 주체의 권한 중첩 구간 = 없음 (위반 횟수 = 0)]</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -865,6 +883,12 @@
       <family val="2"/>
       <charset val="129"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFA31515"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -903,12 +927,15 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -924,6 +951,18 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1248,102 +1287,102 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A1" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="B1" s="4" t="s">
+      <c r="A1" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A2" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A3" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A4" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A5" s="6" t="s">
         <v>66</v>
       </c>
-      <c r="C1" s="4" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A2" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="B2" s="5" t="s">
+      <c r="B5" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A6" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A7" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A8" s="6" t="s">
         <v>68</v>
       </c>
-      <c r="C2" s="5" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A3" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="B3" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="C3" s="5" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A4" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="B4" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A5" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="B5" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="C5" s="5" t="s">
+      <c r="B8" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A9" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="B9" s="6" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A6" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="B6" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="C6" s="5" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A7" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>74</v>
-      </c>
-      <c r="C7" s="5" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A8" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="B8" s="5" t="s">
-        <v>74</v>
-      </c>
-      <c r="C8" s="5" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A9" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="B9" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="C9" s="5" t="s">
-        <v>77</v>
+      <c r="C9" s="6" t="s">
+        <v>81</v>
       </c>
     </row>
   </sheetData>
@@ -1362,190 +1401,190 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A1" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="B1" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="C1" s="4" t="s">
-        <v>78</v>
+      <c r="A1" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>82</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A2" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B2" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="C2" s="5" t="s">
-        <v>79</v>
+      <c r="A2" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A3" s="5" t="s">
+      <c r="A3" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A4" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A5" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A6" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A7" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A8" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A9" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A10" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A11" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="C11" s="6" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A12" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="C12" s="6" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A13" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="C13" s="6" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A14" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="C14" s="6" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A15" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="B15" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="C15" s="6" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A16" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="B16" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="C16" s="6" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A17" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="B3" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="C3" s="5" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A4" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="B4" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A5" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="B5" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A6" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="B6" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="C6" s="5" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A7" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="C7" s="5" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A8" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="B8" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="C8" s="5" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A9" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="B9" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="C9" s="5" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A10" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="B10" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="C10" s="5" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A11" s="5" t="s">
+      <c r="B17" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="B11" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="C11" s="5" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A12" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="B12" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="C12" s="5" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A13" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="B13" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="C13" s="5" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A14" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="B14" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="C14" s="5" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A15" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="B15" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="C15" s="5" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A16" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="B16" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="C16" s="5" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A17" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B17" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="C17" s="5" t="s">
-        <v>94</v>
+      <c r="C17" s="6" t="s">
+        <v>98</v>
       </c>
     </row>
   </sheetData>
@@ -1565,125 +1604,125 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A2" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>98</v>
+      <c r="A2" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>102</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A3" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>99</v>
+      <c r="A3" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>103</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A4" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>139</v>
+      <c r="A4" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>127</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A5" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>101</v>
+      <c r="A5" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>105</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A6" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="C6" s="6" t="s">
-        <v>140</v>
+      <c r="A6" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>128</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A7" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>141</v>
+      <c r="A7" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>129</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A8" s="2"/>
-      <c r="B8" s="2"/>
-      <c r="C8" s="2"/>
+      <c r="A8" s="3"/>
+      <c r="B8" s="3"/>
+      <c r="C8" s="3"/>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A9" s="2"/>
-      <c r="B9" s="2"/>
-      <c r="C9" s="2"/>
+      <c r="A9" s="3"/>
+      <c r="B9" s="3"/>
+      <c r="C9" s="3"/>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A10" s="2"/>
-      <c r="B10" s="2"/>
-      <c r="C10" s="2"/>
+      <c r="A10" s="3"/>
+      <c r="B10" s="3"/>
+      <c r="C10" s="3"/>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A11" s="2"/>
-      <c r="B11" s="2"/>
-      <c r="C11" s="2"/>
+      <c r="A11" s="3"/>
+      <c r="B11" s="3"/>
+      <c r="C11" s="3"/>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A12" s="2"/>
-      <c r="B12" s="2"/>
-      <c r="C12" s="2"/>
+      <c r="A12" s="3"/>
+      <c r="B12" s="3"/>
+      <c r="C12" s="3"/>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A13" s="2"/>
-      <c r="B13" s="2"/>
-      <c r="C13" s="2"/>
+      <c r="A13" s="3"/>
+      <c r="B13" s="3"/>
+      <c r="C13" s="3"/>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A14" s="2"/>
-      <c r="B14" s="2"/>
-      <c r="C14" s="2"/>
+      <c r="A14" s="3"/>
+      <c r="B14" s="3"/>
+      <c r="C14" s="3"/>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A15" s="2"/>
-      <c r="B15" s="2"/>
-      <c r="C15" s="2"/>
+      <c r="A15" s="3"/>
+      <c r="B15" s="3"/>
+      <c r="C15" s="3"/>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A16" s="2"/>
-      <c r="B16" s="2"/>
-      <c r="C16" s="2"/>
+      <c r="A16" s="3"/>
+      <c r="B16" s="3"/>
+      <c r="C16" s="3"/>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
@@ -1704,121 +1743,121 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A2" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>22</v>
+      <c r="A2" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A3" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C3" s="2" t="s">
+      <c r="A3" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A4" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A5" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="B5" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="D3" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A4" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A5" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="C5" s="2" t="s">
+      <c r="C5" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A6" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B6" s="4" t="s">
         <v>106</v>
       </c>
-      <c r="D5" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A6" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>36</v>
+      <c r="C6" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>40</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A7" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>40</v>
+      <c r="A7" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>44</v>
       </c>
     </row>
   </sheetData>
@@ -1838,44 +1877,44 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A2" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>110</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>46</v>
+      <c r="A2" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>50</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A3" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>55</v>
+      <c r="A3" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>59</v>
       </c>
     </row>
   </sheetData>
@@ -1886,186 +1925,353 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{291A8966-D248-40C5-810D-CDD92F7EB876}">
-  <dimension ref="A1:E10"/>
+  <dimension ref="A1:F19"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="2" max="2" width="20.8984375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="67.19921875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="56.69921875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.796875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="99.8984375" customWidth="1"/>
+    <col min="4" max="5" width="5.69921875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="7.19921875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A2" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="B2" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="D2" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="E2" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="F2" s="11" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A3" s="9"/>
+      <c r="B3" s="9"/>
+      <c r="C3" s="8" t="s">
+        <v>132</v>
+      </c>
+      <c r="D3" s="10"/>
+      <c r="E3" s="10"/>
+      <c r="F3" s="11"/>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A4" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="D4" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="E4" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="F4" s="11" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A5" s="9"/>
+      <c r="B5" s="9"/>
+      <c r="C5" s="8" t="s">
+        <v>134</v>
+      </c>
+      <c r="D5" s="10"/>
+      <c r="E5" s="10"/>
+      <c r="F5" s="11"/>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A6" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="D6" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="E6" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="F6" s="11" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A7" s="9"/>
+      <c r="B7" s="9"/>
+      <c r="C7" s="8" t="s">
+        <v>135</v>
+      </c>
+      <c r="D7" s="10"/>
+      <c r="E7" s="11"/>
+      <c r="F7" s="11"/>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A8" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="B8" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="D8" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="E8" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="F8" s="11" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A9" s="9"/>
+      <c r="B9" s="9"/>
+      <c r="C9" s="8" t="s">
+        <v>137</v>
+      </c>
+      <c r="D9" s="11"/>
+      <c r="E9" s="11"/>
+      <c r="F9" s="11"/>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A10" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="B10" s="9" t="s">
+        <v>139</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="D10" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="E10" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="F10" s="11" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A11" s="9"/>
+      <c r="B11" s="9"/>
+      <c r="C11" s="8" t="s">
+        <v>140</v>
+      </c>
+      <c r="D11" s="10"/>
+      <c r="E11" s="10"/>
+      <c r="F11" s="11"/>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A12" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="B12" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="D12" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="E12" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="F12" s="11" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A13" s="9"/>
+      <c r="B13" s="9"/>
+      <c r="C13" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="D13" s="11"/>
+      <c r="E13" s="11"/>
+      <c r="F13" s="11"/>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A14" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="E1" s="1" t="s">
+      <c r="B14" s="9" t="s">
+        <v>142</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="D14" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="E14" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="F14" s="11" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A15" s="9"/>
+      <c r="B15" s="9"/>
+      <c r="C15" s="8" t="s">
+        <v>143</v>
+      </c>
+      <c r="D15" s="11"/>
+      <c r="E15" s="11"/>
+      <c r="F15" s="11"/>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A16" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="B16" s="9" t="s">
+        <v>144</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="D16" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="E16" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="F16" s="11" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A17" s="9"/>
+      <c r="B17" s="9"/>
+      <c r="C17" s="8" t="s">
+        <v>145</v>
+      </c>
+      <c r="D17" s="11"/>
+      <c r="E17" s="11"/>
+      <c r="F17" s="11"/>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A18" s="9" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A2" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A3" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A4" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A5" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A6" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>126</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A7" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A8" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>132</v>
-      </c>
-      <c r="C8" s="2" t="s">
+      <c r="B18" s="9" t="s">
+        <v>146</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="D18" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="E18" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="F18" s="11" t="s">
         <v>133</v>
       </c>
-      <c r="D8" s="2" t="s">
-        <v>134</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A9" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A10" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>45</v>
-      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A19" s="9"/>
+      <c r="B19" s="9"/>
+      <c r="C19" s="8" t="s">
+        <v>148</v>
+      </c>
+      <c r="D19" s="10"/>
+      <c r="E19" s="10"/>
+      <c r="F19" s="11"/>
     </row>
   </sheetData>
+  <mergeCells count="45">
+    <mergeCell ref="A18:A19"/>
+    <mergeCell ref="B18:B19"/>
+    <mergeCell ref="D18:D19"/>
+    <mergeCell ref="E18:E19"/>
+    <mergeCell ref="F18:F19"/>
+    <mergeCell ref="A14:A15"/>
+    <mergeCell ref="B14:B15"/>
+    <mergeCell ref="D14:D15"/>
+    <mergeCell ref="E14:E15"/>
+    <mergeCell ref="F14:F15"/>
+    <mergeCell ref="A16:A17"/>
+    <mergeCell ref="B16:B17"/>
+    <mergeCell ref="D16:D17"/>
+    <mergeCell ref="E16:E17"/>
+    <mergeCell ref="F16:F17"/>
+    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="B10:B11"/>
+    <mergeCell ref="D10:D11"/>
+    <mergeCell ref="E10:E11"/>
+    <mergeCell ref="F10:F11"/>
+    <mergeCell ref="A12:A13"/>
+    <mergeCell ref="B12:B13"/>
+    <mergeCell ref="D12:D13"/>
+    <mergeCell ref="E12:E13"/>
+    <mergeCell ref="F12:F13"/>
+    <mergeCell ref="A6:A7"/>
+    <mergeCell ref="B6:B7"/>
+    <mergeCell ref="D6:D7"/>
+    <mergeCell ref="E6:E7"/>
+    <mergeCell ref="F6:F7"/>
+    <mergeCell ref="A8:A9"/>
+    <mergeCell ref="B8:B9"/>
+    <mergeCell ref="D8:D9"/>
+    <mergeCell ref="E8:E9"/>
+    <mergeCell ref="F8:F9"/>
+    <mergeCell ref="A2:A3"/>
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="D2:D3"/>
+    <mergeCell ref="E2:E3"/>
+    <mergeCell ref="F2:F3"/>
+    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="D4:D5"/>
+    <mergeCell ref="E4:E5"/>
+    <mergeCell ref="F4:F5"/>
+  </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
